--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.ВР Ведомость воздухораспределителей.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.ВР Ведомость воздухораспределителей.xlsx
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>в КСД щелевой решётки ЩП блока К (см. ниже)</t>
+          <t>в переход у фланца блока К → ЩП (см. ниже)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>в КСД щелевой решётки ЩП блока К (см. ниже)</t>
+          <t>в переход у фланца блока К → ЩП (см. ниже)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>в КСД щелевой решётки ЩП блока К (см. ниже)</t>
+          <t>в переход у фланца блока К → ЩП (см. ниже)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>в КСД щелевой решётки ЩП блока К (см. ниже)</t>
+          <t>в воздуховод возврата К-7 → ЩП (см. ниже)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>через ЩП вместе с воздухом блока К</t>
+          <t>через К-7 и ЩП</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>щелевая решётка ЩП 800×150 в стене, через КСД</t>
+          <t>щелевая решётка ЩП 800×150 в подшивке над шкафами, через КСД</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>щелевая решётка ЩВ 800×150 в стене, через КСД</t>
+          <t>щелевая решётка ЩВ 800×150 в подшивке над шкафами, через КСД</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>щелевая решётка ЩП 800×150 в стене, через КСД</t>
+          <t>щелевая решётка ЩП 800×150 в подшивке над шкафами, через КСД</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>щелевая решётка ЩВ 800×150 в стене, через КСД</t>
+          <t>щелевая решётка ЩВ 800×150 в подшивке над шкафами, через КСД</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>щелевая решётка ЩП 800×150 в стене, через КСД</t>
+          <t>щелевая решётка ЩП 800×150 в подшивке над шкафами, через КСД</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>щелевая решётка ЩВ 800×150 в стене, через КСД</t>
+          <t>щелевая решётка ЩВ 800×150 в подшивке над шкафами, через КСД</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>щелевая решётка ЩП 800×150 в стене, через КСД</t>
+          <t>щелевая решётка ЩП 800×150 в стене 2.6/2.7, через КСД</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>щелевая решётка ЩВ 800×150 в стене, через КСД</t>
+          <t>щелевая решётка ЩВ 800×150 в стене 2.6/2.7, через КСД</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
